--- a/debt.xlsx
+++ b/debt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{714C87DA-3CBA-4B51-84A6-A7E798230461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A75AFF-13E2-4B9D-8688-6CDC6A5C3047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t>Аббос Бедана</t>
   </si>
@@ -917,22 +917,13 @@
   </si>
   <si>
     <t>-17 029 827,50</t>
-  </si>
-  <si>
-    <t>Итого</t>
-  </si>
-  <si>
-    <t>-940 145 322,27</t>
-  </si>
-  <si>
-    <t>22 886 406,63</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -944,11 +935,6 @@
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="8"/>
@@ -991,21 +977,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1289,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C163"/>
   <sheetFormatPr defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
@@ -2764,17 +2744,6 @@
       </c>
       <c r="C163" s="2"/>
     </row>
-    <row r="164" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
